--- a/ram.xlsx
+++ b/ram.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\Web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97347E0F-3E04-4527-B0DE-67706074C457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDE48BF8-F5E7-4717-B7C0-91FEAD59D797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/ram.xlsx
+++ b/ram.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\Web\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDE48BF8-F5E7-4717-B7C0-91FEAD59D797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B013AC5F-1EBA-4A3A-948F-9A7A45E47DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1361,9 +1361,6 @@
     <t>2024-08-19 00:12:28</t>
   </si>
   <si>
-    <t>2024-08-19 00:12:40</t>
-  </si>
-  <si>
     <t>connect to rmipclx.com</t>
   </si>
   <si>
@@ -1903,6 +1900,9 @@
   </si>
   <si>
     <t>EXTRACTED_IP</t>
+  </si>
+  <si>
+    <t>2025-04-19 00:12:40</t>
   </si>
 </sst>
 </file>
@@ -1958,11 +1958,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2270,10 +2274,12 @@
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
+    <col min="3" max="3" width="21.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="61.7109375" customWidth="1"/>
     <col min="6" max="6" width="19.5703125" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="22.7109375" customWidth="1"/>
+    <col min="8" max="8" width="47.85546875" style="3" customWidth="1"/>
     <col min="9" max="9" width="16.85546875" customWidth="1"/>
     <col min="10" max="10" width="17.140625" customWidth="1"/>
     <col min="11" max="11" width="38.28515625" bestFit="1" customWidth="1"/>
@@ -2301,17 +2307,17 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>623</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>624</v>
       </c>
       <c r="L1" s="1"/>
     </row>
@@ -2337,7 +2343,7 @@
       <c r="G2" t="s">
         <v>30</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I2" t="s">
@@ -2347,7 +2353,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -2372,7 +2378,7 @@
       <c r="G3" t="s">
         <v>30</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="3" t="s">
         <v>37</v>
       </c>
       <c r="I3" t="s">
@@ -2382,7 +2388,7 @@
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -2407,17 +2413,17 @@
       <c r="G4" t="s">
         <v>30</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="3" t="s">
         <v>40</v>
       </c>
       <c r="I4" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="J4">
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
@@ -2442,7 +2448,7 @@
       <c r="G5" t="s">
         <v>30</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="3" t="s">
         <v>45</v>
       </c>
       <c r="I5" t="s">
@@ -2452,7 +2458,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -2477,7 +2483,7 @@
       <c r="G6" t="s">
         <v>30</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="3" t="s">
         <v>50</v>
       </c>
       <c r="I6" t="s">
@@ -2487,7 +2493,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -2512,7 +2518,7 @@
       <c r="G7" t="s">
         <v>30</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="3" t="s">
         <v>55</v>
       </c>
       <c r="I7" t="s">
@@ -2522,7 +2528,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -2547,17 +2553,17 @@
       <c r="G8" t="s">
         <v>30</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="3" t="s">
         <v>57</v>
       </c>
       <c r="I8" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="J8">
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -2582,7 +2588,7 @@
       <c r="G9" t="s">
         <v>30</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="3" t="s">
         <v>61</v>
       </c>
       <c r="I9" t="s">
@@ -2592,7 +2598,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -2617,7 +2623,7 @@
       <c r="G10" t="s">
         <v>30</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="3" t="s">
         <v>66</v>
       </c>
       <c r="I10" t="s">
@@ -2627,7 +2633,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
@@ -2652,7 +2658,7 @@
       <c r="G11" t="s">
         <v>30</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" s="3" t="s">
         <v>70</v>
       </c>
       <c r="I11" t="s">
@@ -2662,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -2687,7 +2693,7 @@
       <c r="G12" t="s">
         <v>30</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" s="3" t="s">
         <v>75</v>
       </c>
       <c r="I12" t="s">
@@ -2697,7 +2703,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -2722,7 +2728,7 @@
       <c r="G13" t="s">
         <v>30</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="3" t="s">
         <v>75</v>
       </c>
       <c r="I13" t="s">
@@ -2732,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
@@ -2757,7 +2763,7 @@
       <c r="G14" t="s">
         <v>30</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" s="3" t="s">
         <v>75</v>
       </c>
       <c r="I14" t="s">
@@ -2767,7 +2773,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -2792,7 +2798,7 @@
       <c r="G15" t="s">
         <v>30</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" s="3" t="s">
         <v>75</v>
       </c>
       <c r="I15" t="s">
@@ -2802,7 +2808,7 @@
         <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
@@ -2827,7 +2833,7 @@
       <c r="G16" t="s">
         <v>30</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="3" t="s">
         <v>86</v>
       </c>
       <c r="I16" t="s">
@@ -2837,7 +2843,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -2862,7 +2868,7 @@
       <c r="G17" t="s">
         <v>30</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" s="3" t="s">
         <v>86</v>
       </c>
       <c r="I17" t="s">
@@ -2872,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -2897,7 +2903,7 @@
       <c r="G18" t="s">
         <v>30</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" s="3" t="s">
         <v>86</v>
       </c>
       <c r="I18" t="s">
@@ -2907,7 +2913,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -2932,7 +2938,7 @@
       <c r="G19" t="s">
         <v>30</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H19" s="3" t="s">
         <v>94</v>
       </c>
       <c r="I19" t="s">
@@ -2942,7 +2948,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -2967,7 +2973,7 @@
       <c r="G20" t="s">
         <v>30</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H20" s="3" t="s">
         <v>97</v>
       </c>
       <c r="I20" t="s">
@@ -2977,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -3002,7 +3008,7 @@
       <c r="G21" t="s">
         <v>30</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H21" s="3" t="s">
         <v>99</v>
       </c>
       <c r="I21" t="s">
@@ -3012,7 +3018,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -3037,7 +3043,7 @@
       <c r="G22" t="s">
         <v>30</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H22" s="3" t="s">
         <v>104</v>
       </c>
       <c r="I22" t="s">
@@ -3047,7 +3053,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -3072,7 +3078,7 @@
       <c r="G23" t="s">
         <v>30</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H23" s="3" t="s">
         <v>109</v>
       </c>
       <c r="I23" t="s">
@@ -3082,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -3107,7 +3113,7 @@
       <c r="G24" t="s">
         <v>30</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H24" s="3" t="s">
         <v>114</v>
       </c>
       <c r="I24" t="s">
@@ -3117,7 +3123,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -3142,7 +3148,7 @@
       <c r="G25" t="s">
         <v>30</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H25" s="3" t="s">
         <v>116</v>
       </c>
       <c r="I25" t="s">
@@ -3152,7 +3158,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -3177,7 +3183,7 @@
       <c r="G26" t="s">
         <v>30</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H26" s="3" t="s">
         <v>116</v>
       </c>
       <c r="I26" t="s">
@@ -3187,7 +3193,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -3212,7 +3218,7 @@
       <c r="G27" t="s">
         <v>30</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H27" s="3" t="s">
         <v>122</v>
       </c>
       <c r="I27" t="s">
@@ -3222,7 +3228,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -3247,7 +3253,7 @@
       <c r="G28" t="s">
         <v>30</v>
       </c>
-      <c r="H28" t="s">
+      <c r="H28" s="3" t="s">
         <v>124</v>
       </c>
       <c r="I28" t="s">
@@ -3257,7 +3263,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -3282,7 +3288,7 @@
       <c r="G29" t="s">
         <v>30</v>
       </c>
-      <c r="H29" t="s">
+      <c r="H29" s="3" t="s">
         <v>126</v>
       </c>
       <c r="I29" t="s">
@@ -3292,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -3317,7 +3323,7 @@
       <c r="G30" t="s">
         <v>30</v>
       </c>
-      <c r="H30" t="s">
+      <c r="H30" s="3" t="s">
         <v>131</v>
       </c>
       <c r="I30" t="s">
@@ -3327,7 +3333,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -3352,7 +3358,7 @@
       <c r="G31" t="s">
         <v>30</v>
       </c>
-      <c r="H31" t="s">
+      <c r="H31" s="3" t="s">
         <v>133</v>
       </c>
       <c r="I31" t="s">
@@ -3362,7 +3368,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -3387,7 +3393,7 @@
       <c r="G32" t="s">
         <v>30</v>
       </c>
-      <c r="H32" t="s">
+      <c r="H32" s="3" t="s">
         <v>138</v>
       </c>
       <c r="I32" t="s">
@@ -3397,7 +3403,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -3422,7 +3428,7 @@
       <c r="G33" t="s">
         <v>30</v>
       </c>
-      <c r="H33" t="s">
+      <c r="H33" s="3" t="s">
         <v>141</v>
       </c>
       <c r="I33" t="s">
@@ -3432,7 +3438,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -3457,7 +3463,7 @@
       <c r="G34" t="s">
         <v>30</v>
       </c>
-      <c r="H34" t="s">
+      <c r="H34" s="3" t="s">
         <v>146</v>
       </c>
       <c r="I34" t="s">
@@ -3467,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -3492,7 +3498,7 @@
       <c r="G35" t="s">
         <v>30</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H35" s="3" t="s">
         <v>150</v>
       </c>
       <c r="I35" t="s">
@@ -3502,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -3527,7 +3533,7 @@
       <c r="G36" t="s">
         <v>30</v>
       </c>
-      <c r="H36" t="s">
+      <c r="H36" s="3" t="s">
         <v>155</v>
       </c>
       <c r="I36" t="s">
@@ -3537,7 +3543,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -3562,7 +3568,7 @@
       <c r="G37" t="s">
         <v>30</v>
       </c>
-      <c r="H37" t="s">
+      <c r="H37" s="3" t="s">
         <v>159</v>
       </c>
       <c r="I37" t="s">
@@ -3572,7 +3578,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -3597,7 +3603,7 @@
       <c r="G38" t="s">
         <v>30</v>
       </c>
-      <c r="H38" t="s">
+      <c r="H38" s="3" t="s">
         <v>163</v>
       </c>
       <c r="I38" t="s">
@@ -3607,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -3632,7 +3638,7 @@
       <c r="G39" t="s">
         <v>30</v>
       </c>
-      <c r="H39" t="s">
+      <c r="H39" s="3" t="s">
         <v>168</v>
       </c>
       <c r="I39" t="s">
@@ -3642,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -3667,7 +3673,7 @@
       <c r="G40" t="s">
         <v>30</v>
       </c>
-      <c r="H40" t="s">
+      <c r="H40" s="3" t="s">
         <v>168</v>
       </c>
       <c r="I40" t="s">
@@ -3677,7 +3683,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -3702,7 +3708,7 @@
       <c r="G41" t="s">
         <v>30</v>
       </c>
-      <c r="H41" t="s">
+      <c r="H41" s="3" t="s">
         <v>171</v>
       </c>
       <c r="I41" t="s">
@@ -3712,7 +3718,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -3737,7 +3743,7 @@
       <c r="G42" t="s">
         <v>30</v>
       </c>
-      <c r="H42" t="s">
+      <c r="H42" s="3" t="s">
         <v>173</v>
       </c>
       <c r="I42" t="s">
@@ -3747,7 +3753,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -3772,7 +3778,7 @@
       <c r="G43" t="s">
         <v>30</v>
       </c>
-      <c r="H43" t="s">
+      <c r="H43" s="3" t="s">
         <v>173</v>
       </c>
       <c r="I43" t="s">
@@ -3782,7 +3788,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -3807,7 +3813,7 @@
       <c r="G44" t="s">
         <v>30</v>
       </c>
-      <c r="H44" t="s">
+      <c r="H44" s="3" t="s">
         <v>179</v>
       </c>
       <c r="I44" t="s">
@@ -3817,7 +3823,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -3842,7 +3848,7 @@
       <c r="G45" t="s">
         <v>30</v>
       </c>
-      <c r="H45" t="s">
+      <c r="H45" s="3" t="s">
         <v>184</v>
       </c>
       <c r="I45" t="s">
@@ -3852,7 +3858,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -3877,7 +3883,7 @@
       <c r="G46" t="s">
         <v>30</v>
       </c>
-      <c r="H46" t="s">
+      <c r="H46" s="3" t="s">
         <v>188</v>
       </c>
       <c r="I46" t="s">
@@ -3887,7 +3893,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -3912,7 +3918,7 @@
       <c r="G47" t="s">
         <v>30</v>
       </c>
-      <c r="H47" t="s">
+      <c r="H47" s="3" t="s">
         <v>190</v>
       </c>
       <c r="I47" t="s">
@@ -3922,7 +3928,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -3947,7 +3953,7 @@
       <c r="G48" t="s">
         <v>30</v>
       </c>
-      <c r="H48" t="s">
+      <c r="H48" s="3" t="s">
         <v>191</v>
       </c>
       <c r="I48" t="s">
@@ -3957,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -3982,7 +3988,7 @@
       <c r="G49" t="s">
         <v>30</v>
       </c>
-      <c r="H49" t="s">
+      <c r="H49" s="3" t="s">
         <v>195</v>
       </c>
       <c r="I49" t="s">
@@ -3992,7 +3998,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -4017,7 +4023,7 @@
       <c r="G50" t="s">
         <v>30</v>
       </c>
-      <c r="H50" t="s">
+      <c r="H50" s="3" t="s">
         <v>196</v>
       </c>
       <c r="I50" t="s">
@@ -4027,7 +4033,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -4052,7 +4058,7 @@
       <c r="G51" t="s">
         <v>30</v>
       </c>
-      <c r="H51" t="s">
+      <c r="H51" s="3" t="s">
         <v>201</v>
       </c>
       <c r="I51" t="s">
@@ -4062,7 +4068,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -4087,7 +4093,7 @@
       <c r="G52" t="s">
         <v>30</v>
       </c>
-      <c r="H52" t="s">
+      <c r="H52" s="3" t="s">
         <v>205</v>
       </c>
       <c r="I52" t="s">
@@ -4097,7 +4103,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -4122,7 +4128,7 @@
       <c r="G53" t="s">
         <v>30</v>
       </c>
-      <c r="H53" t="s">
+      <c r="H53" s="3" t="s">
         <v>210</v>
       </c>
       <c r="I53" t="s">
@@ -4132,7 +4138,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -4157,7 +4163,7 @@
       <c r="G54" t="s">
         <v>30</v>
       </c>
-      <c r="H54" t="s">
+      <c r="H54" s="3" t="s">
         <v>215</v>
       </c>
       <c r="I54" t="s">
@@ -4167,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -4192,7 +4198,7 @@
       <c r="G55" t="s">
         <v>30</v>
       </c>
-      <c r="H55" t="s">
+      <c r="H55" s="3" t="s">
         <v>219</v>
       </c>
       <c r="I55" t="s">
@@ -4202,7 +4208,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -4227,7 +4233,7 @@
       <c r="G56" t="s">
         <v>30</v>
       </c>
-      <c r="H56" t="s">
+      <c r="H56" s="3" t="s">
         <v>223</v>
       </c>
       <c r="I56" t="s">
@@ -4237,7 +4243,7 @@
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -4262,7 +4268,7 @@
       <c r="G57" t="s">
         <v>30</v>
       </c>
-      <c r="H57" t="s">
+      <c r="H57" s="3" t="s">
         <v>225</v>
       </c>
       <c r="I57" t="s">
@@ -4272,7 +4278,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -4297,7 +4303,7 @@
       <c r="G58" t="s">
         <v>30</v>
       </c>
-      <c r="H58" t="s">
+      <c r="H58" s="3" t="s">
         <v>230</v>
       </c>
       <c r="I58" t="s">
@@ -4307,7 +4313,7 @@
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -4332,7 +4338,7 @@
       <c r="G59" t="s">
         <v>30</v>
       </c>
-      <c r="H59" t="s">
+      <c r="H59" s="3" t="s">
         <v>232</v>
       </c>
       <c r="I59" t="s">
@@ -4342,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -4367,7 +4373,7 @@
       <c r="G60" t="s">
         <v>30</v>
       </c>
-      <c r="H60" t="s">
+      <c r="H60" s="3" t="s">
         <v>236</v>
       </c>
       <c r="I60" t="s">
@@ -4377,7 +4383,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -4402,7 +4408,7 @@
       <c r="G61" t="s">
         <v>30</v>
       </c>
-      <c r="H61" t="s">
+      <c r="H61" s="3" t="s">
         <v>236</v>
       </c>
       <c r="I61" t="s">
@@ -4412,7 +4418,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -4437,7 +4443,7 @@
       <c r="G62" t="s">
         <v>30</v>
       </c>
-      <c r="H62" t="s">
+      <c r="H62" s="3" t="s">
         <v>244</v>
       </c>
       <c r="I62" t="s">
@@ -4447,7 +4453,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -4472,7 +4478,7 @@
       <c r="G63" t="s">
         <v>30</v>
       </c>
-      <c r="H63" t="s">
+      <c r="H63" s="3" t="s">
         <v>248</v>
       </c>
       <c r="I63" t="s">
@@ -4482,7 +4488,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -4507,7 +4513,7 @@
       <c r="G64" t="s">
         <v>30</v>
       </c>
-      <c r="H64" t="s">
+      <c r="H64" s="3" t="s">
         <v>248</v>
       </c>
       <c r="I64" t="s">
@@ -4517,7 +4523,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -4542,7 +4548,7 @@
       <c r="G65" t="s">
         <v>30</v>
       </c>
-      <c r="H65" t="s">
+      <c r="H65" s="3" t="s">
         <v>254</v>
       </c>
       <c r="I65" t="s">
@@ -4552,7 +4558,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -4577,7 +4583,7 @@
       <c r="G66" t="s">
         <v>30</v>
       </c>
-      <c r="H66" t="s">
+      <c r="H66" s="3" t="s">
         <v>256</v>
       </c>
       <c r="I66" t="s">
@@ -4587,7 +4593,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -4612,7 +4618,7 @@
       <c r="G67" t="s">
         <v>30</v>
       </c>
-      <c r="H67" t="s">
+      <c r="H67" s="3" t="s">
         <v>261</v>
       </c>
       <c r="I67" t="s">
@@ -4622,7 +4628,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -4647,7 +4653,7 @@
       <c r="G68" t="s">
         <v>30</v>
       </c>
-      <c r="H68" t="s">
+      <c r="H68" s="3" t="s">
         <v>266</v>
       </c>
       <c r="I68" t="s">
@@ -4657,7 +4663,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -4682,7 +4688,7 @@
       <c r="G69" t="s">
         <v>30</v>
       </c>
-      <c r="H69" t="s">
+      <c r="H69" s="3" t="s">
         <v>269</v>
       </c>
       <c r="I69" t="s">
@@ -4692,7 +4698,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -4717,7 +4723,7 @@
       <c r="G70" t="s">
         <v>30</v>
       </c>
-      <c r="H70" t="s">
+      <c r="H70" s="3" t="s">
         <v>19</v>
       </c>
       <c r="I70" t="s">
@@ -4752,7 +4758,7 @@
       <c r="G71" t="s">
         <v>30</v>
       </c>
-      <c r="H71" t="s">
+      <c r="H71" s="3" t="s">
         <v>273</v>
       </c>
       <c r="I71" t="s">
@@ -4762,7 +4768,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -4787,7 +4793,7 @@
       <c r="G72" t="s">
         <v>30</v>
       </c>
-      <c r="H72" t="s">
+      <c r="H72" s="3" t="s">
         <v>277</v>
       </c>
       <c r="I72" t="s">
@@ -4797,7 +4803,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -4822,7 +4828,7 @@
       <c r="G73" t="s">
         <v>30</v>
       </c>
-      <c r="H73" t="s">
+      <c r="H73" s="3" t="s">
         <v>281</v>
       </c>
       <c r="I73" t="s">
@@ -4832,7 +4838,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -4857,7 +4863,7 @@
       <c r="G74" t="s">
         <v>30</v>
       </c>
-      <c r="H74" t="s">
+      <c r="H74" s="3" t="s">
         <v>285</v>
       </c>
       <c r="I74" t="s">
@@ -4867,7 +4873,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -4892,7 +4898,7 @@
       <c r="G75" t="s">
         <v>30</v>
       </c>
-      <c r="H75" t="s">
+      <c r="H75" s="3" t="s">
         <v>288</v>
       </c>
       <c r="I75" t="s">
@@ -4902,7 +4908,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -4927,7 +4933,7 @@
       <c r="G76" t="s">
         <v>30</v>
       </c>
-      <c r="H76" t="s">
+      <c r="H76" s="3" t="s">
         <v>293</v>
       </c>
       <c r="I76" t="s">
@@ -4937,7 +4943,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -4962,7 +4968,7 @@
       <c r="G77" t="s">
         <v>30</v>
       </c>
-      <c r="H77" t="s">
+      <c r="H77" s="3" t="s">
         <v>298</v>
       </c>
       <c r="I77" t="s">
@@ -4972,7 +4978,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -4997,7 +5003,7 @@
       <c r="G78" t="s">
         <v>30</v>
       </c>
-      <c r="H78" t="s">
+      <c r="H78" s="3" t="s">
         <v>302</v>
       </c>
       <c r="I78" t="s">
@@ -5007,7 +5013,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -5032,7 +5038,7 @@
       <c r="G79" t="s">
         <v>30</v>
       </c>
-      <c r="H79" t="s">
+      <c r="H79" s="3" t="s">
         <v>307</v>
       </c>
       <c r="I79" t="s">
@@ -5042,7 +5048,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -5067,7 +5073,7 @@
       <c r="G80" t="s">
         <v>30</v>
       </c>
-      <c r="H80" t="s">
+      <c r="H80" s="3" t="s">
         <v>308</v>
       </c>
       <c r="I80" t="s">
@@ -5077,7 +5083,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -5102,7 +5108,7 @@
       <c r="G81" t="s">
         <v>30</v>
       </c>
-      <c r="H81" t="s">
+      <c r="H81" s="3" t="s">
         <v>308</v>
       </c>
       <c r="I81" t="s">
@@ -5112,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -5137,7 +5143,7 @@
       <c r="G82" t="s">
         <v>30</v>
       </c>
-      <c r="H82" t="s">
+      <c r="H82" s="3" t="s">
         <v>310</v>
       </c>
       <c r="I82" t="s">
@@ -5147,7 +5153,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -5172,7 +5178,7 @@
       <c r="G83" t="s">
         <v>30</v>
       </c>
-      <c r="H83" t="s">
+      <c r="H83" s="3" t="s">
         <v>25</v>
       </c>
       <c r="I83" t="s">
@@ -5182,7 +5188,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -5207,7 +5213,7 @@
       <c r="G84" t="s">
         <v>30</v>
       </c>
-      <c r="H84" t="s">
+      <c r="H84" s="3" t="s">
         <v>25</v>
       </c>
       <c r="I84" t="s">
@@ -5217,7 +5223,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -5242,7 +5248,7 @@
       <c r="G85" t="s">
         <v>30</v>
       </c>
-      <c r="H85" t="s">
+      <c r="H85" s="3" t="s">
         <v>25</v>
       </c>
       <c r="I85" t="s">
@@ -5252,7 +5258,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -5277,7 +5283,7 @@
       <c r="G86" t="s">
         <v>30</v>
       </c>
-      <c r="H86" t="s">
+      <c r="H86" s="3" t="s">
         <v>25</v>
       </c>
       <c r="I86" t="s">
@@ -5312,7 +5318,7 @@
       <c r="G87" t="s">
         <v>30</v>
       </c>
-      <c r="H87" t="s">
+      <c r="H87" s="3" t="s">
         <v>318</v>
       </c>
       <c r="I87" t="s">
@@ -5322,7 +5328,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
@@ -5347,7 +5353,7 @@
       <c r="G88" t="s">
         <v>30</v>
       </c>
-      <c r="H88" t="s">
+      <c r="H88" s="3" t="s">
         <v>322</v>
       </c>
       <c r="I88" t="s">
@@ -5357,7 +5363,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -5382,7 +5388,7 @@
       <c r="G89" t="s">
         <v>30</v>
       </c>
-      <c r="H89" t="s">
+      <c r="H89" s="3" t="s">
         <v>327</v>
       </c>
       <c r="I89" t="s">
@@ -5392,7 +5398,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -5417,7 +5423,7 @@
       <c r="G90" t="s">
         <v>30</v>
       </c>
-      <c r="H90" t="s">
+      <c r="H90" s="3" t="s">
         <v>331</v>
       </c>
       <c r="I90" t="s">
@@ -5427,7 +5433,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -5452,7 +5458,7 @@
       <c r="G91" t="s">
         <v>30</v>
       </c>
-      <c r="H91" t="s">
+      <c r="H91" s="3" t="s">
         <v>335</v>
       </c>
       <c r="I91" t="s">
@@ -5462,7 +5468,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
@@ -5487,7 +5493,7 @@
       <c r="G92" t="s">
         <v>30</v>
       </c>
-      <c r="H92" t="s">
+      <c r="H92" s="3" t="s">
         <v>339</v>
       </c>
       <c r="I92" t="s">
@@ -5497,7 +5503,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -5522,7 +5528,7 @@
       <c r="G93" t="s">
         <v>30</v>
       </c>
-      <c r="H93" t="s">
+      <c r="H93" s="3" t="s">
         <v>343</v>
       </c>
       <c r="I93" t="s">
@@ -5532,7 +5538,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -5557,7 +5563,7 @@
       <c r="G94" t="s">
         <v>30</v>
       </c>
-      <c r="H94" t="s">
+      <c r="H94" s="3" t="s">
         <v>343</v>
       </c>
       <c r="I94" t="s">
@@ -5567,7 +5573,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -5592,7 +5598,7 @@
       <c r="G95" t="s">
         <v>30</v>
       </c>
-      <c r="H95" t="s">
+      <c r="H95" s="3" t="s">
         <v>346</v>
       </c>
       <c r="I95" t="s">
@@ -5602,7 +5608,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -5627,7 +5633,7 @@
       <c r="G96" t="s">
         <v>30</v>
       </c>
-      <c r="H96" t="s">
+      <c r="H96" s="3" t="s">
         <v>351</v>
       </c>
       <c r="I96" t="s">
@@ -5637,7 +5643,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -5662,7 +5668,7 @@
       <c r="G97" t="s">
         <v>30</v>
       </c>
-      <c r="H97" t="s">
+      <c r="H97" s="3" t="s">
         <v>352</v>
       </c>
       <c r="I97" t="s">
@@ -5672,7 +5678,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
@@ -5697,7 +5703,7 @@
       <c r="G98" t="s">
         <v>30</v>
       </c>
-      <c r="H98" t="s">
+      <c r="H98" s="3" t="s">
         <v>355</v>
       </c>
       <c r="I98" t="s">
@@ -5707,7 +5713,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
@@ -5732,7 +5738,7 @@
       <c r="G99" t="s">
         <v>30</v>
       </c>
-      <c r="H99" t="s">
+      <c r="H99" s="3" t="s">
         <v>359</v>
       </c>
       <c r="I99" t="s">
@@ -5742,7 +5748,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
@@ -5767,7 +5773,7 @@
       <c r="G100" t="s">
         <v>30</v>
       </c>
-      <c r="H100" t="s">
+      <c r="H100" s="3" t="s">
         <v>363</v>
       </c>
       <c r="I100" t="s">
@@ -5777,7 +5783,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
@@ -5802,7 +5808,7 @@
       <c r="G101" t="s">
         <v>30</v>
       </c>
-      <c r="H101" t="s">
+      <c r="H101" s="3" t="s">
         <v>363</v>
       </c>
       <c r="I101" t="s">
@@ -5812,7 +5818,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
@@ -5837,7 +5843,7 @@
       <c r="G102" t="s">
         <v>30</v>
       </c>
-      <c r="H102" t="s">
+      <c r="H102" s="3" t="s">
         <v>363</v>
       </c>
       <c r="I102" t="s">
@@ -5847,7 +5853,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
@@ -5872,7 +5878,7 @@
       <c r="G103" t="s">
         <v>30</v>
       </c>
-      <c r="H103" t="s">
+      <c r="H103" s="3" t="s">
         <v>369</v>
       </c>
       <c r="I103" t="s">
@@ -5882,7 +5888,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
@@ -5907,7 +5913,7 @@
       <c r="G104" t="s">
         <v>30</v>
       </c>
-      <c r="H104" t="s">
+      <c r="H104" s="3" t="s">
         <v>374</v>
       </c>
       <c r="I104" t="s">
@@ -5917,7 +5923,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
@@ -5942,7 +5948,7 @@
       <c r="G105" t="s">
         <v>30</v>
       </c>
-      <c r="H105" t="s">
+      <c r="H105" s="3" t="s">
         <v>378</v>
       </c>
       <c r="I105" t="s">
@@ -5952,7 +5958,7 @@
         <v>0</v>
       </c>
       <c r="K105" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
@@ -5977,7 +5983,7 @@
       <c r="G106" t="s">
         <v>30</v>
       </c>
-      <c r="H106" t="s">
+      <c r="H106" s="3" t="s">
         <v>382</v>
       </c>
       <c r="I106" t="s">
@@ -5987,7 +5993,7 @@
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
@@ -6012,7 +6018,7 @@
       <c r="G107" t="s">
         <v>30</v>
       </c>
-      <c r="H107" t="s">
+      <c r="H107" s="3" t="s">
         <v>384</v>
       </c>
       <c r="I107" t="s">
@@ -6022,7 +6028,7 @@
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
@@ -6047,7 +6053,7 @@
       <c r="G108" t="s">
         <v>30</v>
       </c>
-      <c r="H108" t="s">
+      <c r="H108" s="3" t="s">
         <v>389</v>
       </c>
       <c r="I108" t="s">
@@ -6057,7 +6063,7 @@
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
@@ -6082,7 +6088,7 @@
       <c r="G109" t="s">
         <v>30</v>
       </c>
-      <c r="H109" t="s">
+      <c r="H109" s="3" t="s">
         <v>391</v>
       </c>
       <c r="I109" t="s">
@@ -6092,7 +6098,7 @@
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
@@ -6117,7 +6123,7 @@
       <c r="G110" t="s">
         <v>30</v>
       </c>
-      <c r="H110" t="s">
+      <c r="H110" s="3" t="s">
         <v>392</v>
       </c>
       <c r="I110" t="s">
@@ -6127,7 +6133,7 @@
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
@@ -6152,7 +6158,7 @@
       <c r="G111" t="s">
         <v>30</v>
       </c>
-      <c r="H111" t="s">
+      <c r="H111" s="3" t="s">
         <v>396</v>
       </c>
       <c r="I111" t="s">
@@ -6162,7 +6168,7 @@
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
@@ -6187,7 +6193,7 @@
       <c r="G112" t="s">
         <v>30</v>
       </c>
-      <c r="H112" t="s">
+      <c r="H112" s="3" t="s">
         <v>398</v>
       </c>
       <c r="I112" t="s">
@@ -6197,7 +6203,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
@@ -6222,7 +6228,7 @@
       <c r="G113" t="s">
         <v>30</v>
       </c>
-      <c r="H113" t="s">
+      <c r="H113" s="3" t="s">
         <v>402</v>
       </c>
       <c r="I113" t="s">
@@ -6232,7 +6238,7 @@
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
@@ -6257,7 +6263,7 @@
       <c r="G114" t="s">
         <v>30</v>
       </c>
-      <c r="H114" t="s">
+      <c r="H114" s="3" t="s">
         <v>402</v>
       </c>
       <c r="I114" t="s">
@@ -6267,7 +6273,7 @@
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
@@ -6292,7 +6298,7 @@
       <c r="G115" t="s">
         <v>30</v>
       </c>
-      <c r="H115" t="s">
+      <c r="H115" s="3" t="s">
         <v>408</v>
       </c>
       <c r="I115" t="s">
@@ -6302,7 +6308,7 @@
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
@@ -6327,7 +6333,7 @@
       <c r="G116" t="s">
         <v>30</v>
       </c>
-      <c r="H116" t="s">
+      <c r="H116" s="3" t="s">
         <v>410</v>
       </c>
       <c r="I116" t="s">
@@ -6337,7 +6343,7 @@
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
@@ -6362,7 +6368,7 @@
       <c r="G117" t="s">
         <v>30</v>
       </c>
-      <c r="H117" t="s">
+      <c r="H117" s="3" t="s">
         <v>410</v>
       </c>
       <c r="I117" t="s">
@@ -6372,7 +6378,7 @@
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
@@ -6397,7 +6403,7 @@
       <c r="G118" t="s">
         <v>30</v>
       </c>
-      <c r="H118" t="s">
+      <c r="H118" s="3" t="s">
         <v>412</v>
       </c>
       <c r="I118" t="s">
@@ -6407,7 +6413,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
@@ -6432,7 +6438,7 @@
       <c r="G119" t="s">
         <v>30</v>
       </c>
-      <c r="H119" t="s">
+      <c r="H119" s="3" t="s">
         <v>416</v>
       </c>
       <c r="I119" t="s">
@@ -6442,7 +6448,7 @@
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
@@ -6467,7 +6473,7 @@
       <c r="G120" t="s">
         <v>30</v>
       </c>
-      <c r="H120" t="s">
+      <c r="H120" s="3" t="s">
         <v>417</v>
       </c>
       <c r="I120" t="s">
@@ -6477,7 +6483,7 @@
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
@@ -6502,7 +6508,7 @@
       <c r="G121" t="s">
         <v>30</v>
       </c>
-      <c r="H121" t="s">
+      <c r="H121" s="3" t="s">
         <v>422</v>
       </c>
       <c r="I121" t="s">
@@ -6512,7 +6518,7 @@
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
@@ -6537,7 +6543,7 @@
       <c r="G122" t="s">
         <v>30</v>
       </c>
-      <c r="H122" t="s">
+      <c r="H122" s="3" t="s">
         <v>422</v>
       </c>
       <c r="I122" t="s">
@@ -6547,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="K122" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
@@ -6572,7 +6578,7 @@
       <c r="G123" t="s">
         <v>30</v>
       </c>
-      <c r="H123" t="s">
+      <c r="H123" s="3" t="s">
         <v>429</v>
       </c>
       <c r="I123" t="s">
@@ -6582,7 +6588,7 @@
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
@@ -6607,7 +6613,7 @@
       <c r="G124" t="s">
         <v>30</v>
       </c>
-      <c r="H124" t="s">
+      <c r="H124" s="3" t="s">
         <v>434</v>
       </c>
       <c r="I124" t="s">
@@ -6617,7 +6623,7 @@
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
@@ -6642,7 +6648,7 @@
       <c r="G125" t="s">
         <v>30</v>
       </c>
-      <c r="H125" t="s">
+      <c r="H125" s="3" t="s">
         <v>436</v>
       </c>
       <c r="I125" t="s">
@@ -6652,7 +6658,7 @@
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
@@ -6677,7 +6683,7 @@
       <c r="G126" t="s">
         <v>30</v>
       </c>
-      <c r="H126" t="s">
+      <c r="H126" s="3" t="s">
         <v>441</v>
       </c>
       <c r="I126" t="s">
@@ -6687,7 +6693,7 @@
         <v>0</v>
       </c>
       <c r="K126" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
@@ -6712,7 +6718,7 @@
       <c r="G127" t="s">
         <v>30</v>
       </c>
-      <c r="H127" t="s">
+      <c r="H127" s="3" t="s">
         <v>444</v>
       </c>
       <c r="I127" t="s">
@@ -6722,7 +6728,7 @@
         <v>0</v>
       </c>
       <c r="K127" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
@@ -6747,25 +6753,25 @@
       <c r="G128" t="s">
         <v>30</v>
       </c>
-      <c r="H128" t="s">
+      <c r="H128" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="I128" t="s">
         <v>445</v>
       </c>
-      <c r="I128" t="s">
-        <v>446</v>
-      </c>
       <c r="J128">
         <v>0</v>
       </c>
       <c r="K128" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
+        <v>446</v>
+      </c>
+      <c r="B129" t="s">
         <v>447</v>
-      </c>
-      <c r="B129" t="s">
-        <v>448</v>
       </c>
       <c r="C129" t="s">
         <v>178</v>
@@ -6782,8 +6788,8 @@
       <c r="G129" t="s">
         <v>30</v>
       </c>
-      <c r="H129" t="s">
-        <v>449</v>
+      <c r="H129" s="3" t="s">
+        <v>448</v>
       </c>
       <c r="I129" t="s">
         <v>289</v>
@@ -6792,15 +6798,15 @@
         <v>0</v>
       </c>
       <c r="K129" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
+        <v>449</v>
+      </c>
+      <c r="B130" t="s">
         <v>450</v>
-      </c>
-      <c r="B130" t="s">
-        <v>451</v>
       </c>
       <c r="C130" t="s">
         <v>388</v>
@@ -6817,43 +6823,43 @@
       <c r="G130" t="s">
         <v>30</v>
       </c>
-      <c r="H130" t="s">
+      <c r="H130" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="I130" t="s">
         <v>452</v>
       </c>
-      <c r="I130" t="s">
-        <v>453</v>
-      </c>
       <c r="J130">
         <v>0</v>
       </c>
       <c r="K130" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
+        <v>453</v>
+      </c>
+      <c r="B131" t="s">
         <v>454</v>
       </c>
-      <c r="B131" t="s">
+      <c r="C131" t="s">
         <v>455</v>
       </c>
-      <c r="C131" t="s">
+      <c r="D131" t="s">
+        <v>12</v>
+      </c>
+      <c r="E131" t="s">
+        <v>455</v>
+      </c>
+      <c r="F131" t="s">
+        <v>13</v>
+      </c>
+      <c r="G131" t="s">
+        <v>30</v>
+      </c>
+      <c r="H131" s="3" t="s">
         <v>456</v>
-      </c>
-      <c r="D131" t="s">
-        <v>12</v>
-      </c>
-      <c r="E131" t="s">
-        <v>456</v>
-      </c>
-      <c r="F131" t="s">
-        <v>13</v>
-      </c>
-      <c r="G131" t="s">
-        <v>30</v>
-      </c>
-      <c r="H131" t="s">
-        <v>457</v>
       </c>
       <c r="I131" t="s">
         <v>360</v>
@@ -6862,15 +6868,15 @@
         <v>0</v>
       </c>
       <c r="K131" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>457</v>
+      </c>
+      <c r="B132" t="s">
         <v>458</v>
-      </c>
-      <c r="B132" t="s">
-        <v>459</v>
       </c>
       <c r="C132" t="s">
         <v>433</v>
@@ -6887,8 +6893,8 @@
       <c r="G132" t="s">
         <v>30</v>
       </c>
-      <c r="H132" t="s">
-        <v>457</v>
+      <c r="H132" s="3" t="s">
+        <v>456</v>
       </c>
       <c r="I132" t="s">
         <v>151</v>
@@ -6897,15 +6903,15 @@
         <v>0</v>
       </c>
       <c r="K132" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>459</v>
+      </c>
+      <c r="B133" t="s">
         <v>460</v>
-      </c>
-      <c r="B133" t="s">
-        <v>461</v>
       </c>
       <c r="C133" t="s">
         <v>154</v>
@@ -6922,8 +6928,8 @@
       <c r="G133" t="s">
         <v>30</v>
       </c>
-      <c r="H133" t="s">
-        <v>462</v>
+      <c r="H133" s="3" t="s">
+        <v>461</v>
       </c>
       <c r="I133" t="s">
         <v>77</v>
@@ -6932,7 +6938,7 @@
         <v>0</v>
       </c>
       <c r="K133" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
@@ -6940,7 +6946,7 @@
         <v>26</v>
       </c>
       <c r="B134" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C134" t="s">
         <v>29</v>
@@ -6957,8 +6963,8 @@
       <c r="G134" t="s">
         <v>30</v>
       </c>
-      <c r="H134" t="s">
-        <v>462</v>
+      <c r="H134" s="3" t="s">
+        <v>461</v>
       </c>
       <c r="I134" t="s">
         <v>77</v>
@@ -6967,15 +6973,15 @@
         <v>0</v>
       </c>
       <c r="K134" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
+        <v>463</v>
+      </c>
+      <c r="B135" t="s">
         <v>464</v>
-      </c>
-      <c r="B135" t="s">
-        <v>465</v>
       </c>
       <c r="C135" t="s">
         <v>154</v>
@@ -6992,8 +6998,8 @@
       <c r="G135" t="s">
         <v>30</v>
       </c>
-      <c r="H135" t="s">
-        <v>466</v>
+      <c r="H135" s="3" t="s">
+        <v>465</v>
       </c>
       <c r="I135" t="s">
         <v>110</v>
@@ -7002,42 +7008,42 @@
         <v>0</v>
       </c>
       <c r="K135" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
+        <v>466</v>
+      </c>
+      <c r="B136" t="s">
         <v>467</v>
       </c>
-      <c r="B136" t="s">
+      <c r="C136" t="s">
         <v>468</v>
       </c>
-      <c r="C136" t="s">
+      <c r="D136" t="s">
+        <v>12</v>
+      </c>
+      <c r="E136" t="s">
+        <v>468</v>
+      </c>
+      <c r="F136" t="s">
+        <v>13</v>
+      </c>
+      <c r="G136" t="s">
+        <v>30</v>
+      </c>
+      <c r="H136" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="D136" t="s">
-        <v>12</v>
-      </c>
-      <c r="E136" t="s">
-        <v>469</v>
-      </c>
-      <c r="F136" t="s">
-        <v>13</v>
-      </c>
-      <c r="G136" t="s">
-        <v>30</v>
-      </c>
-      <c r="H136" t="s">
+      <c r="I136" t="s">
         <v>470</v>
       </c>
-      <c r="I136" t="s">
-        <v>471</v>
-      </c>
       <c r="J136">
         <v>0</v>
       </c>
       <c r="K136" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
@@ -7062,8 +7068,8 @@
       <c r="G137" t="s">
         <v>30</v>
       </c>
-      <c r="H137" t="s">
-        <v>472</v>
+      <c r="H137" s="3" t="s">
+        <v>471</v>
       </c>
       <c r="I137" t="s">
         <v>132</v>
@@ -7072,15 +7078,15 @@
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
+        <v>472</v>
+      </c>
+      <c r="B138" t="s">
         <v>473</v>
-      </c>
-      <c r="B138" t="s">
-        <v>474</v>
       </c>
       <c r="C138" t="s">
         <v>358</v>
@@ -7097,8 +7103,8 @@
       <c r="G138" t="s">
         <v>30</v>
       </c>
-      <c r="H138" t="s">
-        <v>475</v>
+      <c r="H138" s="3" t="s">
+        <v>474</v>
       </c>
       <c r="I138" t="s">
         <v>38</v>
@@ -7107,7 +7113,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
@@ -7132,8 +7138,8 @@
       <c r="G139" t="s">
         <v>30</v>
       </c>
-      <c r="H139" t="s">
-        <v>475</v>
+      <c r="H139" s="3" t="s">
+        <v>474</v>
       </c>
       <c r="I139" t="s">
         <v>360</v>
@@ -7142,15 +7148,15 @@
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>475</v>
+      </c>
+      <c r="B140" t="s">
         <v>476</v>
-      </c>
-      <c r="B140" t="s">
-        <v>477</v>
       </c>
       <c r="C140" t="s">
         <v>65</v>
@@ -7167,52 +7173,52 @@
       <c r="G140" t="s">
         <v>30</v>
       </c>
-      <c r="H140" t="s">
+      <c r="H140" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="I140" t="s">
         <v>478</v>
       </c>
-      <c r="I140" t="s">
-        <v>479</v>
-      </c>
       <c r="J140">
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
+        <v>479</v>
+      </c>
+      <c r="B141" t="s">
         <v>480</v>
       </c>
-      <c r="B141" t="s">
+      <c r="C141" t="s">
         <v>481</v>
       </c>
-      <c r="C141" t="s">
+      <c r="D141" t="s">
+        <v>12</v>
+      </c>
+      <c r="E141" t="s">
+        <v>481</v>
+      </c>
+      <c r="F141" t="s">
+        <v>13</v>
+      </c>
+      <c r="G141" t="s">
+        <v>30</v>
+      </c>
+      <c r="H141" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="I141" t="s">
         <v>482</v>
       </c>
-      <c r="D141" t="s">
-        <v>12</v>
-      </c>
-      <c r="E141" t="s">
-        <v>482</v>
-      </c>
-      <c r="F141" t="s">
-        <v>13</v>
-      </c>
-      <c r="G141" t="s">
-        <v>30</v>
-      </c>
-      <c r="H141" t="s">
-        <v>478</v>
-      </c>
-      <c r="I141" t="s">
-        <v>483</v>
-      </c>
       <c r="J141">
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
@@ -7237,25 +7243,25 @@
       <c r="G142" t="s">
         <v>30</v>
       </c>
-      <c r="H142" t="s">
+      <c r="H142" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="I142" t="s">
         <v>484</v>
       </c>
-      <c r="I142" t="s">
-        <v>485</v>
-      </c>
       <c r="J142">
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
+        <v>485</v>
+      </c>
+      <c r="B143" t="s">
         <v>486</v>
-      </c>
-      <c r="B143" t="s">
-        <v>487</v>
       </c>
       <c r="C143" t="s">
         <v>29</v>
@@ -7272,8 +7278,8 @@
       <c r="G143" t="s">
         <v>30</v>
       </c>
-      <c r="H143" t="s">
-        <v>488</v>
+      <c r="H143" s="3" t="s">
+        <v>487</v>
       </c>
       <c r="I143" t="s">
         <v>95</v>
@@ -7282,85 +7288,85 @@
         <v>0</v>
       </c>
       <c r="K143" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
+        <v>488</v>
+      </c>
+      <c r="B144" t="s">
         <v>489</v>
       </c>
-      <c r="B144" t="s">
+      <c r="C144" t="s">
         <v>490</v>
       </c>
-      <c r="C144" t="s">
+      <c r="D144" t="s">
+        <v>12</v>
+      </c>
+      <c r="E144" t="s">
+        <v>490</v>
+      </c>
+      <c r="F144" t="s">
+        <v>13</v>
+      </c>
+      <c r="G144" t="s">
+        <v>30</v>
+      </c>
+      <c r="H144" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="D144" t="s">
-        <v>12</v>
-      </c>
-      <c r="E144" t="s">
-        <v>491</v>
-      </c>
-      <c r="F144" t="s">
-        <v>13</v>
-      </c>
-      <c r="G144" t="s">
-        <v>30</v>
-      </c>
-      <c r="H144" t="s">
-        <v>492</v>
-      </c>
       <c r="I144" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J144">
         <v>0</v>
       </c>
       <c r="K144" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
+        <v>492</v>
+      </c>
+      <c r="B145" t="s">
         <v>493</v>
       </c>
-      <c r="B145" t="s">
+      <c r="C145" t="s">
         <v>494</v>
       </c>
-      <c r="C145" t="s">
+      <c r="D145" t="s">
+        <v>12</v>
+      </c>
+      <c r="E145" t="s">
+        <v>494</v>
+      </c>
+      <c r="F145" t="s">
+        <v>13</v>
+      </c>
+      <c r="G145" t="s">
+        <v>30</v>
+      </c>
+      <c r="H145" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="D145" t="s">
-        <v>12</v>
-      </c>
-      <c r="E145" t="s">
-        <v>495</v>
-      </c>
-      <c r="F145" t="s">
-        <v>13</v>
-      </c>
-      <c r="G145" t="s">
-        <v>30</v>
-      </c>
-      <c r="H145" t="s">
+      <c r="I145" t="s">
         <v>496</v>
       </c>
-      <c r="I145" t="s">
-        <v>497</v>
-      </c>
       <c r="J145">
         <v>0</v>
       </c>
       <c r="K145" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
+        <v>497</v>
+      </c>
+      <c r="B146" t="s">
         <v>498</v>
-      </c>
-      <c r="B146" t="s">
-        <v>499</v>
       </c>
       <c r="C146" t="s">
         <v>194</v>
@@ -7377,8 +7383,8 @@
       <c r="G146" t="s">
         <v>30</v>
       </c>
-      <c r="H146" t="s">
-        <v>500</v>
+      <c r="H146" s="3" t="s">
+        <v>499</v>
       </c>
       <c r="I146" t="s">
         <v>62</v>
@@ -7387,15 +7393,15 @@
         <v>0</v>
       </c>
       <c r="K146" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
+        <v>500</v>
+      </c>
+      <c r="B147" t="s">
         <v>501</v>
-      </c>
-      <c r="B147" t="s">
-        <v>502</v>
       </c>
       <c r="C147" t="s">
         <v>292</v>
@@ -7412,60 +7418,60 @@
       <c r="G147" t="s">
         <v>30</v>
       </c>
-      <c r="H147" t="s">
+      <c r="H147" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="I147" t="s">
         <v>503</v>
       </c>
-      <c r="I147" t="s">
-        <v>504</v>
-      </c>
       <c r="J147">
         <v>0</v>
       </c>
       <c r="K147" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
+        <v>504</v>
+      </c>
+      <c r="B148" t="s">
         <v>505</v>
       </c>
-      <c r="B148" t="s">
+      <c r="C148" t="s">
         <v>506</v>
       </c>
-      <c r="C148" t="s">
+      <c r="D148" t="s">
+        <v>12</v>
+      </c>
+      <c r="E148" t="s">
+        <v>506</v>
+      </c>
+      <c r="F148" t="s">
+        <v>13</v>
+      </c>
+      <c r="G148" t="s">
+        <v>30</v>
+      </c>
+      <c r="H148" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="I148" t="s">
         <v>507</v>
       </c>
-      <c r="D148" t="s">
-        <v>12</v>
-      </c>
-      <c r="E148" t="s">
-        <v>507</v>
-      </c>
-      <c r="F148" t="s">
-        <v>13</v>
-      </c>
-      <c r="G148" t="s">
-        <v>30</v>
-      </c>
-      <c r="H148" t="s">
-        <v>503</v>
-      </c>
-      <c r="I148" t="s">
-        <v>508</v>
-      </c>
       <c r="J148">
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
+        <v>508</v>
+      </c>
+      <c r="B149" t="s">
         <v>509</v>
-      </c>
-      <c r="B149" t="s">
-        <v>510</v>
       </c>
       <c r="C149" t="s">
         <v>218</v>
@@ -7482,8 +7488,8 @@
       <c r="G149" t="s">
         <v>30</v>
       </c>
-      <c r="H149" t="s">
-        <v>503</v>
+      <c r="H149" s="3" t="s">
+        <v>502</v>
       </c>
       <c r="I149" t="s">
         <v>132</v>
@@ -7492,15 +7498,15 @@
         <v>0</v>
       </c>
       <c r="K149" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
+        <v>510</v>
+      </c>
+      <c r="B150" t="s">
         <v>511</v>
-      </c>
-      <c r="B150" t="s">
-        <v>512</v>
       </c>
       <c r="C150" t="s">
         <v>222</v>
@@ -7517,8 +7523,8 @@
       <c r="G150" t="s">
         <v>30</v>
       </c>
-      <c r="H150" t="s">
-        <v>513</v>
+      <c r="H150" s="3" t="s">
+        <v>512</v>
       </c>
       <c r="I150" t="s">
         <v>110</v>
@@ -7527,15 +7533,15 @@
         <v>0</v>
       </c>
       <c r="K150" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
+        <v>513</v>
+      </c>
+      <c r="B151" t="s">
         <v>514</v>
-      </c>
-      <c r="B151" t="s">
-        <v>515</v>
       </c>
       <c r="C151" t="s">
         <v>253</v>
@@ -7552,8 +7558,8 @@
       <c r="G151" t="s">
         <v>30</v>
       </c>
-      <c r="H151" t="s">
-        <v>516</v>
+      <c r="H151" s="3" t="s">
+        <v>515</v>
       </c>
       <c r="I151" t="s">
         <v>255</v>
@@ -7562,59 +7568,59 @@
         <v>0</v>
       </c>
       <c r="K151" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
+        <v>516</v>
+      </c>
+      <c r="B152" t="s">
         <v>517</v>
       </c>
-      <c r="B152" t="s">
+      <c r="C152" t="s">
+        <v>494</v>
+      </c>
+      <c r="D152" t="s">
+        <v>12</v>
+      </c>
+      <c r="E152" t="s">
+        <v>494</v>
+      </c>
+      <c r="F152" t="s">
+        <v>13</v>
+      </c>
+      <c r="G152" t="s">
+        <v>30</v>
+      </c>
+      <c r="H152" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="C152" t="s">
-        <v>495</v>
-      </c>
-      <c r="D152" t="s">
-        <v>12</v>
-      </c>
-      <c r="E152" t="s">
-        <v>495</v>
-      </c>
-      <c r="F152" t="s">
-        <v>13</v>
-      </c>
-      <c r="G152" t="s">
-        <v>30</v>
-      </c>
-      <c r="H152" t="s">
+      <c r="I152" t="s">
         <v>519</v>
       </c>
-      <c r="I152" t="s">
-        <v>520</v>
-      </c>
       <c r="J152">
         <v>0</v>
       </c>
       <c r="K152" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
+        <v>520</v>
+      </c>
+      <c r="B153" t="s">
         <v>521</v>
       </c>
-      <c r="B153" t="s">
+      <c r="C153" t="s">
         <v>522</v>
       </c>
-      <c r="C153" t="s">
-        <v>523</v>
-      </c>
       <c r="D153" t="s">
         <v>12</v>
       </c>
       <c r="E153" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="F153" t="s">
         <v>13</v>
@@ -7622,8 +7628,8 @@
       <c r="G153" t="s">
         <v>30</v>
       </c>
-      <c r="H153" t="s">
-        <v>519</v>
+      <c r="H153" s="3" t="s">
+        <v>518</v>
       </c>
       <c r="I153" t="s">
         <v>430</v>
@@ -7632,7 +7638,7 @@
         <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
   </sheetData>

--- a/ram.xlsx
+++ b/ram.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\Web\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\STMNC\STMNC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B013AC5F-1EBA-4A3A-948F-9A7A45E47DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB276E2-F781-4DB2-987F-710733005F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,33 +22,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1531" uniqueCount="625">
   <si>
-    <t>MAC</t>
-  </si>
-  <si>
-    <t>IP</t>
-  </si>
-  <si>
-    <t>UNIT_NAME</t>
-  </si>
-  <si>
-    <t>USER_NAME</t>
-  </si>
-  <si>
-    <t>UNIT_FULL_NAME</t>
-  </si>
-  <si>
-    <t>ALERT_TYPE</t>
-  </si>
-  <si>
-    <t>ALERT_LEVEL_ID</t>
-  </si>
-  <si>
-    <t>TIME_RECEIVE</t>
-  </si>
-  <si>
-    <t>DESCRIPTION</t>
-  </si>
-  <si>
     <t>08-BF-B8-35-9F-E8</t>
   </si>
   <si>
@@ -1896,13 +1869,40 @@
     <t>connect to 46.247.108.221</t>
   </si>
   <si>
-    <t>LABEL</t>
-  </si>
-  <si>
-    <t>EXTRACTED_IP</t>
-  </si>
-  <si>
     <t>2025-04-19 00:12:40</t>
+  </si>
+  <si>
+    <t>mac</t>
+  </si>
+  <si>
+    <t>ip</t>
+  </si>
+  <si>
+    <t>unit_name</t>
+  </si>
+  <si>
+    <t>user_name</t>
+  </si>
+  <si>
+    <t>unit_full_name</t>
+  </si>
+  <si>
+    <t>alert_type</t>
+  </si>
+  <si>
+    <t>alert_level_id</t>
+  </si>
+  <si>
+    <t>time_receive</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>label</t>
+  </si>
+  <si>
+    <t>extracted_ip</t>
   </si>
 </sst>
 </file>
@@ -2278,7 +2278,7 @@
     <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="61.7109375" customWidth="1"/>
     <col min="6" max="6" width="19.5703125" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="7" max="7" width="24" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="47.85546875" style="3" customWidth="1"/>
     <col min="9" max="9" width="16.85546875" customWidth="1"/>
     <col min="10" max="10" width="17.140625" customWidth="1"/>
@@ -2287,5358 +2287,5358 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>614</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>615</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>616</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>617</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>618</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>619</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>620</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>7</v>
+        <v>621</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>622</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L1" s="1"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="I2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="I3" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E4" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="I4" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="J4">
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" t="s">
         <v>35</v>
       </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>44</v>
-      </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="I5" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J5">
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="I6" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="J6">
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G7" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="I7" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="J7">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G8" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="I8" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="J8">
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G9" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="I9" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="J9">
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G10" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="I10" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G11" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="I11" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G12" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="I12" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="J12">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E13" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G13" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="I13" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E14" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G14" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="I14" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E15" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G15" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="I15" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="J15">
         <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D16" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G16" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I16" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D17" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E17" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F17" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G17" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I17" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D18" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E18" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F18" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G18" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I18" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J18">
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="B19" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D19" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E19" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="F19" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G19" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="I19" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E20" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F20" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G20" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="I20" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D21" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E21" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F21" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G21" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="I21" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="J21">
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D22" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E22" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="F22" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G22" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="I22" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="J22">
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="B23" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="C23" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D23" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E23" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="F23" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G23" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="I23" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="J23">
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="B24" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C24" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D24" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E24" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="F24" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G24" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="I24" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B25" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C25" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D25" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E25" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="F25" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G25" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="I25" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C26" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D26" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E26" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F26" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G26" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="I26" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="J26">
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C27" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D27" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E27" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="F27" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G27" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="I27" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="J27">
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D28" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E28" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="F28" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G28" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="I28" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="B29" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D29" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E29" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="F29" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G29" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="I29" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="J29">
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="B30" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D30" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E30" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="F30" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G30" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="I30" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="J30">
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" t="s">
         <v>26</v>
       </c>
-      <c r="B31" t="s">
-        <v>27</v>
-      </c>
-      <c r="C31" t="s">
-        <v>35</v>
-      </c>
       <c r="D31" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E31" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F31" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G31" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="I31" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="J31">
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="B32" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="C32" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D32" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E32" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="F32" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G32" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="I32" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="J32">
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="B33" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="C33" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D33" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E33" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="F33" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G33" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="I33" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="J33">
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="B34" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="C34" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D34" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E34" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="F34" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G34" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="I34" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="J34">
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="B35" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C35" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D35" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E35" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="F35" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G35" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="I35" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="J35">
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="B36" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="C36" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D36" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E36" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F36" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G36" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="I36" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="J36">
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="B37" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="C37" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D37" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E37" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F37" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G37" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="I37" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="J37">
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="B38" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="C38" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D38" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E38" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="F38" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G38" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="I38" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="J38">
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B39" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C39" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D39" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E39" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="F39" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G39" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="I39" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="J39">
         <v>0</v>
       </c>
       <c r="K39" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="B40" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="C40" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E40" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F40" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G40" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="I40" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="J40">
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B41" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C41" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D41" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E41" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F41" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G41" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="I41" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="J41">
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B42" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D42" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E42" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F42" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G42" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="I42" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="J42">
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B43" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C43" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D43" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E43" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F43" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G43" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="I43" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="J43">
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="B44" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="C44" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D44" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E44" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="F44" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G44" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="I44" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="J44">
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B45" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C45" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D45" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E45" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F45" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G45" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="I45" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="J45">
         <v>0</v>
       </c>
       <c r="K45" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="B46" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="C46" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D46" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E46" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F46" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G46" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="I46" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="J46">
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="B47" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="C47" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D47" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E47" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F47" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G47" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="I47" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="J47">
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="B48" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="C48" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D48" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E48" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F48" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G48" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="I48" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="J48">
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="B49" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="C49" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D49" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E49" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="F49" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G49" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="I49" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="J49">
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D50" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E50" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F50" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G50" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="I50" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="J50">
         <v>0</v>
       </c>
       <c r="K50" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="B51" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C51" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D51" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E51" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="F51" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G51" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="I51" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="J51">
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="B52" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="C52" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D52" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E52" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F52" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G52" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="I52" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="J52">
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="B53" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="C53" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D53" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E53" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="F53" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G53" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="I53" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="J53">
         <v>0</v>
       </c>
       <c r="K53" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="B54" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="C54" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D54" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E54" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="F54" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G54" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="I54" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J54">
         <v>0</v>
       </c>
       <c r="K54" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="B55" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="C55" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D55" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E55" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="F55" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G55" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="I55" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="J55">
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="B56" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="C56" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D56" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E56" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="F56" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G56" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="I56" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="J56">
         <v>0</v>
       </c>
       <c r="K56" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>17</v>
+      </c>
+      <c r="B57" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" t="s">
         <v>26</v>
       </c>
-      <c r="B57" t="s">
-        <v>27</v>
-      </c>
-      <c r="C57" t="s">
-        <v>35</v>
-      </c>
       <c r="D57" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E57" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F57" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G57" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="I57" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="J57">
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="B58" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C58" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D58" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E58" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="F58" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G58" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="I58" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="J58">
         <v>0</v>
       </c>
       <c r="K58" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="B59" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C59" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D59" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E59" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="F59" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G59" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="I59" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="J59">
         <v>0</v>
       </c>
       <c r="K59" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="B60" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="C60" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D60" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E60" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="F60" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G60" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="I60" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="J60">
         <v>0</v>
       </c>
       <c r="K60" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="B61" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="C61" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D61" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E61" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="F61" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G61" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="I61" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="J61">
         <v>0</v>
       </c>
       <c r="K61" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="B62" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="C62" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D62" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E62" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F62" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G62" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="I62" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="J62">
         <v>0</v>
       </c>
       <c r="K62" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="B63" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="C63" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D63" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E63" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="F63" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G63" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="I63" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="J63">
         <v>0</v>
       </c>
       <c r="K63" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="B64" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="C64" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D64" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E64" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="F64" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G64" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="I64" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="J64">
         <v>0</v>
       </c>
       <c r="K64" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="B65" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="C65" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D65" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E65" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="F65" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G65" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="I65" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="J65">
         <v>0</v>
       </c>
       <c r="K65" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B66" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C66" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D66" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E66" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F66" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G66" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="I66" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="J66">
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="B67" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="C67" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D67" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E67" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="F67" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G67" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="I67" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="J67">
         <v>0</v>
       </c>
       <c r="K67" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="B68" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="C68" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D68" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E68" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="F68" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G68" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="I68" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="J68">
         <v>0</v>
       </c>
       <c r="K68" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="B69" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="C69" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D69" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E69" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="F69" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G69" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="I69" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="J69">
         <v>0</v>
       </c>
       <c r="K69" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B70" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C70" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D70" t="s">
+        <v>3</v>
+      </c>
+      <c r="E70" t="s">
+        <v>9</v>
+      </c>
+      <c r="F70" t="s">
+        <v>4</v>
+      </c>
+      <c r="G70" t="s">
+        <v>21</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I70" t="s">
+        <v>11</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70" t="s">
         <v>12</v>
-      </c>
-      <c r="E70" t="s">
-        <v>18</v>
-      </c>
-      <c r="F70" t="s">
-        <v>13</v>
-      </c>
-      <c r="G70" t="s">
-        <v>30</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I70" t="s">
-        <v>20</v>
-      </c>
-      <c r="J70">
-        <v>0</v>
-      </c>
-      <c r="K70" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="B71" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C71" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D71" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E71" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="F71" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G71" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="I71" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="J71">
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="B72" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="C72" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D72" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E72" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="F72" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G72" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="I72" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="J72">
         <v>0</v>
       </c>
       <c r="K72" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="B73" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="C73" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D73" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E73" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="F73" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G73" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="I73" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="J73">
         <v>0</v>
       </c>
       <c r="K73" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="B74" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="C74" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D74" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E74" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F74" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G74" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="I74" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="J74">
         <v>0</v>
       </c>
       <c r="K74" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="B75" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="C75" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D75" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E75" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F75" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G75" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="I75" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J75">
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="B76" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="C76" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D76" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E76" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="F76" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G76" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="I76" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="J76">
         <v>0</v>
       </c>
       <c r="K76" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="B77" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C77" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D77" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E77" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="F77" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G77" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="I77" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="J77">
         <v>0</v>
       </c>
       <c r="K77" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="B78" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="C78" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D78" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E78" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="F78" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G78" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="I78" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="J78">
         <v>0</v>
       </c>
       <c r="K78" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="B79" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="C79" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D79" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E79" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="F79" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G79" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="I79" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="J79">
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="B80" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="C80" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D80" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E80" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F80" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G80" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="I80" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="J80">
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B81" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C81" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D81" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E81" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F81" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G81" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="I81" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="J81">
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B82" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C82" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D82" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E82" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F82" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G82" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="I82" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="J82">
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="B83" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="C83" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D83" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E83" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="F83" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G83" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I83" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="J83">
         <v>0</v>
       </c>
       <c r="K83" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="B84" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="C84" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D84" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E84" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F84" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G84" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I84" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="J84">
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B85" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C85" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D85" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E85" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F85" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G85" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I85" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="J85">
         <v>0</v>
       </c>
       <c r="K85" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B86" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C86" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D86" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E86" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F86" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G86" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I86" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J86">
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B87" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="C87" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D87" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E87" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="F87" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G87" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="I87" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="J87">
         <v>0</v>
       </c>
       <c r="K87" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="B88" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="C88" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D88" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E88" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="F88" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G88" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="I88" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="J88">
         <v>0</v>
       </c>
       <c r="K88" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="B89" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="C89" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D89" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E89" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="F89" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G89" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="I89" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="J89">
         <v>0</v>
       </c>
       <c r="K89" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="B90" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="C90" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D90" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E90" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="F90" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G90" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="I90" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J90">
         <v>0</v>
       </c>
       <c r="K90" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="B91" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="C91" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D91" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E91" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="F91" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G91" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="I91" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="J91">
         <v>0</v>
       </c>
       <c r="K91" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="B92" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="C92" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D92" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E92" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="F92" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G92" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="I92" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="J92">
         <v>0</v>
       </c>
       <c r="K92" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="B93" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="C93" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D93" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E93" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F93" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G93" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="I93" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="J93">
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="B94" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="C94" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D94" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E94" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F94" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G94" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="I94" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="J94">
         <v>0</v>
       </c>
       <c r="K94" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="B95" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="C95" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D95" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E95" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="F95" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G95" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="I95" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="J95">
         <v>0</v>
       </c>
       <c r="K95" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="B96" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="C96" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D96" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E96" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="F96" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G96" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="I96" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="J96">
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="B97" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="C97" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D97" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E97" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="F97" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G97" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="I97" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="J97">
         <v>0</v>
       </c>
       <c r="K97" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="B98" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="C98" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D98" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E98" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="F98" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G98" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="I98" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="J98">
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="B99" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="C99" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D99" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E99" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="F99" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G99" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="I99" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="J99">
         <v>0</v>
       </c>
       <c r="K99" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="B100" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="C100" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D100" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E100" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F100" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G100" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="I100" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="J100">
         <v>0</v>
       </c>
       <c r="K100" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="B101" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="C101" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D101" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E101" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F101" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G101" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="I101" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="J101">
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="B102" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="C102" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D102" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E102" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F102" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G102" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="I102" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="J102">
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="B103" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="C103" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D103" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E103" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F103" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G103" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="I103" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="J103">
         <v>0</v>
       </c>
       <c r="K103" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="B104" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="C104" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D104" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E104" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="F104" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G104" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="I104" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="J104">
         <v>0</v>
       </c>
       <c r="K104" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="B105" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="C105" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D105" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E105" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="F105" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G105" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="I105" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="J105">
         <v>0</v>
       </c>
       <c r="K105" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="B106" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C106" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D106" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E106" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="F106" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G106" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="I106" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="J106">
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="B107" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="C107" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D107" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E107" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F107" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G107" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="I107" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="J107">
         <v>0</v>
       </c>
       <c r="K107" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="B108" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="C108" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D108" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E108" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="F108" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G108" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="I108" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="J108">
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="B109" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="C109" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D109" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E109" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="F109" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G109" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="I109" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="J109">
         <v>0</v>
       </c>
       <c r="K109" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="B110" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="C110" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D110" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E110" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="F110" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G110" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="I110" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J110">
         <v>0</v>
       </c>
       <c r="K110" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="B111" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="C111" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D111" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E111" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="F111" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G111" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="I111" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="J111">
         <v>0</v>
       </c>
       <c r="K111" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="B112" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="C112" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D112" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E112" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="F112" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G112" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="I112" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="J112">
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="B113" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="C113" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D113" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E113" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="F113" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G113" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="I113" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="J113">
         <v>0</v>
       </c>
       <c r="K113" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="B114" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="C114" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D114" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E114" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="F114" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G114" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="I114" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="J114">
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="B115" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="C115" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="D115" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E115" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="F115" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G115" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="I115" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="J115">
         <v>0</v>
       </c>
       <c r="K115" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="B116" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="C116" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="D116" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E116" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="F116" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G116" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="I116" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="J116">
         <v>0</v>
       </c>
       <c r="K116" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="B117" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="C117" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="D117" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E117" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="F117" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G117" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="I117" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="J117">
         <v>0</v>
       </c>
       <c r="K117" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B118" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C118" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="D118" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E118" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F118" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G118" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="I118" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="J118">
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="B119" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="C119" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="D119" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E119" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="F119" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G119" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="I119" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="J119">
         <v>0</v>
       </c>
       <c r="K119" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B120" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C120" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D120" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E120" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F120" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G120" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="I120" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="J120">
         <v>0</v>
       </c>
       <c r="K120" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="B121" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="C121" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="D121" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E121" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="F121" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G121" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="I121" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="J121">
         <v>0</v>
       </c>
       <c r="K121" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="B122" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="C122" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D122" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E122" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F122" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G122" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="I122" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="J122">
         <v>0</v>
       </c>
       <c r="K122" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="B123" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="C123" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="D123" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E123" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="F123" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G123" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="I123" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="J123">
         <v>0</v>
       </c>
       <c r="K123" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="B124" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="C124" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="D124" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E124" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="F124" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G124" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="I124" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="J124">
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B125" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C125" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D125" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E125" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F125" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G125" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="I125" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="J125">
         <v>0</v>
       </c>
       <c r="K125" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="B126" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="C126" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="D126" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E126" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="F126" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G126" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="I126" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="J126">
         <v>0</v>
       </c>
       <c r="K126" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="B127" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="C127" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D127" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E127" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F127" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G127" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="I127" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J127">
         <v>0</v>
       </c>
       <c r="K127" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B128" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C128" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D128" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E128" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F128" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G128" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="I128" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="J128">
         <v>0</v>
       </c>
       <c r="K128" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="B129" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="C129" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="D129" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E129" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="F129" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G129" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="I129" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="J129">
         <v>0</v>
       </c>
       <c r="K129" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="B130" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="C130" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="D130" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E130" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="F130" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G130" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="I130" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="J130">
         <v>0</v>
       </c>
       <c r="K130" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="B131" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="C131" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="D131" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E131" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="F131" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G131" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="I131" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="J131">
         <v>0</v>
       </c>
       <c r="K131" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="B132" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="C132" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="D132" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E132" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="F132" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G132" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="I132" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="J132">
         <v>0</v>
       </c>
       <c r="K132" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="B133" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="C133" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="D133" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E133" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F133" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G133" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="I133" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="J133">
         <v>0</v>
       </c>
       <c r="K133" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B134" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="C134" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D134" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E134" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F134" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G134" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="I134" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="J134">
         <v>0</v>
       </c>
       <c r="K134" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="B135" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="C135" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="D135" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E135" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F135" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G135" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="I135" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="J135">
         <v>0</v>
       </c>
       <c r="K135" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="B136" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="C136" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="D136" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E136" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="F136" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G136" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="I136" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="J136">
         <v>0</v>
       </c>
       <c r="K136" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="B137" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="C137" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D137" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E137" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F137" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G137" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="I137" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="J137">
         <v>0</v>
       </c>
       <c r="K137" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="B138" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="C138" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="D138" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E138" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="F138" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G138" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="I138" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="J138">
         <v>0</v>
       </c>
       <c r="K138" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="B139" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="C139" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="D139" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E139" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="F139" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G139" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="I139" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="J139">
         <v>0</v>
       </c>
       <c r="K139" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="B140" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="C140" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D140" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E140" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="F140" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G140" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="I140" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="J140">
         <v>0</v>
       </c>
       <c r="K140" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="B141" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="C141" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="D141" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E141" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="F141" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G141" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="I141" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="J141">
         <v>0</v>
       </c>
       <c r="K141" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="B142" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C142" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D142" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E142" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F142" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G142" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H142" s="3" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="I142" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="J142">
         <v>0</v>
       </c>
       <c r="K142" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="B143" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="C143" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D143" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E143" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F143" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G143" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="I143" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="J143">
         <v>0</v>
       </c>
       <c r="K143" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="B144" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="C144" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="D144" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E144" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="F144" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G144" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="I144" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="J144">
         <v>0</v>
       </c>
       <c r="K144" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="B145" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="C145" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="D145" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E145" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="F145" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G145" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="I145" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="J145">
         <v>0</v>
       </c>
       <c r="K145" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="B146" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="C146" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="D146" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E146" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="F146" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G146" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="I146" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="J146">
         <v>0</v>
       </c>
       <c r="K146" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="B147" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="C147" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="D147" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E147" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="F147" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G147" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="I147" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="J147">
         <v>0</v>
       </c>
       <c r="K147" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="B148" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="C148" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="D148" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E148" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="F148" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G148" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="I148" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="J148">
         <v>0</v>
       </c>
       <c r="K148" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="B149" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="C149" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="D149" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E149" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="F149" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G149" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="I149" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="J149">
         <v>0</v>
       </c>
       <c r="K149" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="B150" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="C150" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="D150" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E150" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="F150" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G150" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="I150" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="J150">
         <v>0</v>
       </c>
       <c r="K150" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="B151" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="C151" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="D151" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E151" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="F151" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G151" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="I151" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="J151">
         <v>0</v>
       </c>
       <c r="K151" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="B152" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="C152" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="D152" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E152" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="F152" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G152" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H152" s="3" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="I152" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="J152">
         <v>0</v>
       </c>
       <c r="K152" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="B153" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="C153" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="D153" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E153" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="F153" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G153" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="H153" s="3" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="I153" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="J153">
         <v>0</v>
       </c>
       <c r="K153" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
     </row>
   </sheetData>
